--- a/docs/StructureDefinition-LTCConditionResidence.xlsx
+++ b/docs/StructureDefinition-LTCConditionResidence.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCConditionResidence.xlsx
+++ b/docs/StructureDefinition-LTCConditionResidence.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCConditionResidence.xlsx
+++ b/docs/StructureDefinition-LTCConditionResidence.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCConditionResidence.xlsx
+++ b/docs/StructureDefinition-LTCConditionResidence.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCConditionResidence.xlsx
+++ b/docs/StructureDefinition-LTCConditionResidence.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$55</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
     <t>0</t>
@@ -527,14 +530,24 @@
     <t>http://hl7.org/fhir/ValueSet/condition-clinical|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>con-3
+con-4con-5</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>&lt; 303105007 |Disease phases|</t>
+  </si>
+  <si>
+    <t>PRB-14</t>
+  </si>
+  <si>
+    <t>Observation ACT
+.inboundRelationship[typeCode=COMP].source[classCode=OBS, code="clinicalStatus", moodCode=EVN].value</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
   </si>
   <si>
     <t>Condition.verificationStatus</t>
@@ -552,6 +565,23 @@
     <t>http://hl7.org/fhir/ValueSet/condition-ver-status|4.0.1</t>
   </si>
   <si>
+    <t>con-3
+con-5</t>
+  </si>
+  <si>
+    <t>&lt; 410514004 |Finding context value|</t>
+  </si>
+  <si>
+    <t>PRB-13</t>
+  </si>
+  <si>
+    <t>Observation ACT
+.inboundRelationship[typeCode=COMP].source[classCode=OBS, code="verificationStatus", moodCode=EVN].value</t>
+  </si>
+  <si>
+    <t>408729009</t>
+  </si>
+  <si>
     <t>Condition.category</t>
   </si>
   <si>
@@ -573,6 +603,18 @@
     <t>http://hl7.org/fhir/ValueSet/condition-category</t>
   </si>
   <si>
+    <t>&lt; 404684003 |Clinical finding|</t>
+  </si>
+  <si>
+    <t>'problem' if from PRB-3. 'diagnosis' if from DG1 segment in PV1 message</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>Condition.severity</t>
   </si>
   <si>
@@ -589,6 +631,21 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+  </si>
+  <si>
+    <t>&lt; 272141005 |Severities|</t>
+  </si>
+  <si>
+    <t>PRB-26 / ABS-3</t>
+  </si>
+  <si>
+    <t>Can be pre/post-coordinated into value.  Or ./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="severity"].value</t>
+  </si>
+  <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
+    <t>246112005</t>
   </si>
   <si>
     <t>Condition.code</t>
@@ -604,13 +661,37 @@
     <t>病情、問題或診斷的識別</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>0..1，主要用於說明敘述性resource。</t>
   </si>
   <si>
     <t>http://ltc-ig.fhir.tw/ValueSet/ReferralConditionResidenceVS-TWLTC</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>code 246090004 |Associated finding| (&lt; 404684003 |Clinical finding| MINUS
+&lt;&lt; 420134006 |Propensity to adverse reactions| MINUS 
+&lt;&lt; 473010000 |Hypersensitivity condition| MINUS 
+&lt;&lt; 79899007 |Drug interaction| MINUS
+&lt;&lt; 69449002 |Drug action| MINUS 
+&lt;&lt; 441742003 |Evaluation finding| MINUS 
+&lt;&lt; 307824009 |Administrative status| MINUS 
+&lt;&lt; 385356007 |Tumor stage finding|) 
+OR &lt; 413350009 |Finding with explicit context|
+OR &lt; 272379006 |Event|</t>
+  </si>
+  <si>
+    <t>PRB-3</t>
+  </si>
+  <si>
+    <t>.value</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>246090004</t>
   </si>
   <si>
     <t>Condition.code.id</t>
@@ -677,10 +758,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
   </si>
   <si>
     <t>Condition.code.coding.id</t>
@@ -942,6 +1023,15 @@
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
+  </si>
+  <si>
+    <t>.targetBodySiteCode</t>
+  </si>
+  <si>
+    <t>363698007</t>
+  </si>
+  <si>
     <t>Condition.subject</t>
   </si>
   <si>
@@ -1178,6 +1268,13 @@
     <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
   </si>
   <si>
+    <t xml:space="preserve">con-1
+</t>
+  </si>
+  <si>
+    <t>&lt; 254291000 |Staging and scales|</t>
+  </si>
+  <si>
     <t>Condition.stage.assessment</t>
   </si>
   <si>
@@ -1191,10 +1288,6 @@
     <t>分期評估所依據的證據之正式記錄</t>
   </si>
   <si>
-    <t xml:space="preserve">con-1
-</t>
-  </si>
-  <si>
     <t>.self</t>
   </si>
   <si>
@@ -1211,6 +1304,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+  </si>
+  <si>
+    <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
   </si>
   <si>
     <t>Condition.evidence</t>
@@ -1256,24 +1352,30 @@
     <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
   </si>
   <si>
-    <t>Condition.evidence.detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>在其他地方找到的支持資訊</t>
-  </si>
-  <si>
-    <t>其他相關資訊的連接，包括病理報告。</t>
-  </si>
-  <si>
     <t xml:space="preserve">con-2
 </t>
   </si>
   <si>
+    <t>Event.reasonCode</t>
+  </si>
+  <si>
+    <t>[code="diagnosis"].value</t>
+  </si>
+  <si>
     <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>Condition.evidence.detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>在其他地方找到的支持資訊</t>
+  </si>
+  <si>
+    <t>其他相關資訊的連接，包括病理報告。</t>
   </si>
   <si>
     <t>Condition.note</t>
@@ -1612,7 +1714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO55"/>
+  <dimension ref="A1:AP55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.99609375" customWidth="true" bestFit="true"/>
@@ -1652,9 +1754,10 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="58.4765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="190.4140625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1781,6 +1884,9 @@
       <c r="AO1" t="s" s="1">
         <v>77</v>
       </c>
+      <c r="AP1" t="s" s="1">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1795,10 +1901,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1810,13 +1916,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1870,39 +1976,42 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1910,10 +2019,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1922,19 +2031,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1984,13 +2093,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2011,15 +2120,18 @@
         <v>20</v>
       </c>
       <c r="AO3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2027,10 +2139,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2039,16 +2151,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2099,19 +2211,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2126,15 +2238,18 @@
         <v>20</v>
       </c>
       <c r="AO4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2142,31 +2257,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2216,19 +2331,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2243,15 +2358,18 @@
         <v>20</v>
       </c>
       <c r="AO5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2259,10 +2377,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2274,16 +2392,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2297,7 +2415,7 @@
         <v>20</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U6" t="s" s="2">
         <v>20</v>
@@ -2309,13 +2427,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2333,19 +2451,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2360,26 +2478,29 @@
         <v>20</v>
       </c>
       <c r="AO6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2391,16 +2512,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2450,19 +2571,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2474,29 +2595,32 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2508,16 +2632,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2567,13 +2691,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2591,29 +2715,32 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2625,16 +2752,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2684,19 +2811,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2708,53 +2835,56 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2803,19 +2933,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2827,18 +2957,21 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2846,10 +2979,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2858,22 +2991,22 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2922,22 +3055,22 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
@@ -2946,18 +3079,21 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
+      </c>
+      <c r="AP11" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2965,31 +3101,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3015,13 +3151,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3039,42 +3175,45 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AO12" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3082,31 +3221,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3132,66 +3271,69 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z13" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="AA13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>167</v>
-      </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
+      </c>
+      <c r="AP13" t="s" s="2">
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3199,13 +3341,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>20</v>
@@ -3214,16 +3356,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3249,13 +3391,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3273,42 +3415,45 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3316,13 +3461,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -3331,16 +3476,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3366,13 +3511,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3390,77 +3535,78 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>202</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3485,11 +3631,11 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3507,42 +3653,45 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>165</v>
+        <v>211</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>20</v>
+        <v>213</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>214</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3550,10 +3699,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3565,13 +3714,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3622,13 +3771,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -3646,18 +3795,21 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AO17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3665,10 +3817,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3680,13 +3832,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3725,31 +3877,31 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3764,15 +3916,18 @@
         <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3780,34 +3935,34 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3844,29 +3999,29 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
@@ -3875,21 +4030,24 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AO19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3897,10 +4055,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3912,13 +4070,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3969,13 +4127,13 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
@@ -3993,18 +4151,21 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AO20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4012,10 +4173,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4027,16 +4188,16 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4074,31 +4235,31 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
@@ -4113,15 +4274,18 @@
         <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4129,34 +4293,34 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4166,7 +4330,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -4205,19 +4369,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -4226,21 +4390,24 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="AO22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4248,10 +4415,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4260,19 +4427,19 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4322,19 +4489,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -4343,21 +4510,24 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4365,32 +4535,32 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4439,19 +4609,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -4460,21 +4630,24 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="AO24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4482,32 +4655,32 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4556,19 +4729,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -4577,21 +4750,24 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="AO25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4599,10 +4775,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4611,22 +4787,22 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4675,19 +4851,19 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
@@ -4696,58 +4872,61 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4772,11 +4951,11 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4794,19 +4973,19 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
@@ -4815,58 +4994,61 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AO27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4891,13 +5073,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -4915,19 +5097,19 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -4936,58 +5118,61 @@
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AO28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5012,13 +5197,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5036,19 +5221,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5057,58 +5242,61 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AO29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5133,11 +5321,11 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5155,19 +5343,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5176,58 +5364,61 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AO30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5252,13 +5443,13 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5276,19 +5467,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5297,58 +5488,61 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AO31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5373,13 +5567,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5397,19 +5591,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5418,21 +5612,24 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AO32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5440,34 +5637,34 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5516,19 +5713,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -5537,21 +5734,24 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="AO33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5559,31 +5759,31 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5609,13 +5809,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5633,75 +5833,78 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>166</v>
+        <v>324</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>325</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5750,42 +5953,45 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>335</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5793,10 +5999,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5805,19 +6011,19 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5867,42 +6073,45 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>318</v>
+        <v>344</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5910,31 +6119,31 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5984,42 +6193,45 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>327</v>
+        <v>353</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6027,13 +6239,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -6042,16 +6254,16 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6101,19 +6313,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6125,18 +6337,21 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>334</v>
+        <v>360</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6144,10 +6359,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6156,16 +6371,16 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6216,19 +6431,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6237,21 +6452,24 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>341</v>
+        <v>367</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6259,10 +6477,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6271,16 +6489,16 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6331,19 +6549,19 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6355,18 +6573,21 @@
         <v>20</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6374,28 +6595,28 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6446,19 +6667,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6467,21 +6688,24 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>353</v>
+        <v>379</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6489,10 +6713,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6504,13 +6728,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6561,19 +6785,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -6585,18 +6809,21 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="AO42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6604,10 +6831,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6619,13 +6846,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6676,13 +6903,13 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
@@ -6700,29 +6927,32 @@
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AO43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6734,16 +6964,16 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6793,19 +7023,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -6817,53 +7047,56 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AO44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6912,19 +7145,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -6936,18 +7169,21 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6955,10 +7191,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6970,17 +7206,15 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7005,13 +7239,13 @@
         <v>20</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7029,42 +7263,45 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>164</v>
+        <v>401</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>20</v>
+        <v>402</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="AO46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7072,10 +7309,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7087,13 +7324,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7144,19 +7381,19 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7168,18 +7405,21 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7187,10 +7427,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7202,17 +7442,15 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7237,13 +7475,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7261,19 +7499,19 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
@@ -7282,21 +7520,24 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>166</v>
+        <v>413</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7304,10 +7545,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7319,16 +7560,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7378,19 +7619,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -7402,18 +7643,21 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7421,10 +7665,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7436,13 +7680,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7493,13 +7737,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -7517,29 +7761,32 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7551,16 +7798,16 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7610,19 +7857,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -7634,53 +7881,56 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="AO51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7729,19 +7979,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -7753,18 +8003,21 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AO52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7772,10 +8025,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>20</v>
@@ -7784,20 +8037,18 @@
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -7822,13 +8073,13 @@
         <v>20</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -7846,42 +8097,45 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>164</v>
+        <v>428</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>166</v>
+        <v>430</v>
       </c>
       <c r="AO53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7889,10 +8143,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -7901,16 +8155,16 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7961,19 +8215,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -7985,18 +8239,21 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>405</v>
+        <v>431</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8004,13 +8261,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>20</v>
@@ -8019,13 +8276,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>409</v>
+        <v>439</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8076,38 +8333,41 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>406</v>
+        <v>436</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>411</v>
+        <v>441</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO55">
+  <autoFilter ref="A1:AP55">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/docs/StructureDefinition-LTCConditionResidence.xlsx
+++ b/docs/StructureDefinition-LTCConditionResidence.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCConditionResidence.xlsx
+++ b/docs/StructureDefinition-LTCConditionResidence.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
